--- a/Output/Final/ValidationMetrics.xlsx
+++ b/Output/Final/ValidationMetrics.xlsx
@@ -476,46 +476,46 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0156262213330963</v>
+        <v>0.0156296885229576</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00134183864083625</v>
+        <v>0.00134507479147935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0238448442767479</v>
+        <v>0.0239660835494127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00494948378219414</v>
+        <v>0.0049559826455553</v>
       </c>
       <c r="I2" t="n">
-        <v>0.607733199612026</v>
+        <v>0.603692992639812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.126840356271898</v>
+        <v>0.127641038548602</v>
       </c>
       <c r="K2" t="n">
-        <v>1954.80499891852</v>
+        <v>1954.80501106873</v>
       </c>
       <c r="L2" t="n">
-        <v>29.1445945913264</v>
+        <v>29.1445926363676</v>
       </c>
       <c r="M2" t="n">
-        <v>1912.75637068868</v>
+        <v>1912.75639523434</v>
       </c>
       <c r="N2" t="n">
-        <v>27.3388912581692</v>
+        <v>27.3388959711821</v>
       </c>
       <c r="O2" t="n">
-        <v>8.97994026984079</v>
+        <v>8.9799378566019</v>
       </c>
       <c r="P2" t="n">
-        <v>0.396035875922865</v>
+        <v>0.39603810359544</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.590524761633849</v>
+        <v>0.58763371263075</v>
       </c>
     </row>
     <row r="3">
@@ -529,46 +529,46 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0159393450548166</v>
+        <v>0.0160867985214279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00125631360355849</v>
+        <v>0.00142130030286652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.024365740687958</v>
+        <v>0.0244718347319619</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00522798308242243</v>
+        <v>0.00538846044705627</v>
       </c>
       <c r="I3" t="n">
-        <v>0.597046979165734</v>
+        <v>0.59657952411417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.134540386062275</v>
+        <v>0.135886725264482</v>
       </c>
       <c r="K3" t="n">
-        <v>1954.59418165191</v>
+        <v>1954.5942129408</v>
       </c>
       <c r="L3" t="n">
-        <v>29.2454658497057</v>
+        <v>29.2455250175506</v>
       </c>
       <c r="M3" t="n">
-        <v>1912.30628245179</v>
+        <v>1912.30633104831</v>
       </c>
       <c r="N3" t="n">
-        <v>27.5150735479072</v>
+        <v>27.5151572945814</v>
       </c>
       <c r="O3" t="n">
-        <v>9.03937901721712</v>
+        <v>9.03937888492493</v>
       </c>
       <c r="P3" t="n">
-        <v>0.373311288877877</v>
+        <v>0.373312543450146</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.574836139524658</v>
+        <v>0.570560578724514</v>
       </c>
     </row>
     <row r="4">
@@ -582,46 +582,46 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0229430806120346</v>
+        <v>0.0229888663934352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00273770077417251</v>
+        <v>0.00259362198349953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0295990506749567</v>
+        <v>0.0297469442922153</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00406732594596503</v>
+        <v>0.00398223981251856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0772379041355462</v>
+        <v>-0.0215003157539895</v>
       </c>
       <c r="J4" t="n">
-        <v>0.154385794093906</v>
+        <v>0.114635473662213</v>
       </c>
       <c r="K4" t="n">
-        <v>1969.98491809351</v>
+        <v>1969.98491037019</v>
       </c>
       <c r="L4" t="n">
-        <v>32.329159562856</v>
+        <v>32.3291841318408</v>
       </c>
       <c r="M4" t="n">
-        <v>1935.27096523024</v>
+        <v>1935.27095560758</v>
       </c>
       <c r="N4" t="n">
-        <v>32.415733121804</v>
+        <v>32.4157610414181</v>
       </c>
       <c r="O4" t="n">
-        <v>10.7843809150791</v>
+        <v>10.7843813154403</v>
       </c>
       <c r="P4" t="n">
-        <v>0.189627262184925</v>
+        <v>0.189629308739532</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0606013007478776</v>
+        <v>-0.0173170456203957</v>
       </c>
     </row>
     <row r="5">
@@ -635,46 +635,46 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0239996276304242</v>
+        <v>0.0240710239854671</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00242264231532917</v>
+        <v>0.00242986353763497</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0300294923253875</v>
+        <v>0.0300702325370642</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00377713861654925</v>
+        <v>0.00388605543385344</v>
       </c>
       <c r="I5" t="n">
-        <v>0.184945142030356</v>
+        <v>0.187806095485241</v>
       </c>
       <c r="J5" t="n">
-        <v>0.119785478250916</v>
+        <v>0.113186478931942</v>
       </c>
       <c r="K5" t="n">
-        <v>1972.36041103104</v>
+        <v>1972.36051747327</v>
       </c>
       <c r="L5" t="n">
-        <v>32.2365794206212</v>
+        <v>32.2364310319874</v>
       </c>
       <c r="M5" t="n">
-        <v>1939.68709271891</v>
+        <v>1939.68723499729</v>
       </c>
       <c r="N5" t="n">
-        <v>32.2215747887788</v>
+        <v>32.2213849233279</v>
       </c>
       <c r="O5" t="n">
-        <v>10.7064607666018</v>
+        <v>10.7064556500184</v>
       </c>
       <c r="P5" t="n">
-        <v>0.218931311852044</v>
+        <v>0.218921603869167</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.186091152259047</v>
+        <v>0.184819122403118</v>
       </c>
     </row>
     <row r="6">
@@ -688,46 +688,46 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0266645501692423</v>
+        <v>0.0266651882499642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00397803903193285</v>
+        <v>0.00397601628812348</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0372956356474325</v>
+        <v>0.0372969314812794</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00599458704590787</v>
+        <v>0.00599128819421142</v>
       </c>
       <c r="I6" t="n">
-        <v>0.116168324594857</v>
+        <v>0.116149870450902</v>
       </c>
       <c r="J6" t="n">
-        <v>0.11730985092128</v>
+        <v>0.11731469572898</v>
       </c>
       <c r="K6" t="n">
-        <v>-130190.613645011</v>
+        <v>-130190.613645609</v>
       </c>
       <c r="L6" t="n">
-        <v>16023.5157805856</v>
+        <v>16023.5157804007</v>
       </c>
       <c r="M6" t="n">
-        <v>965741.63483519</v>
+        <v>965741.634681007</v>
       </c>
       <c r="N6" t="n">
-        <v>368818.243667074</v>
+        <v>368818.243684431</v>
       </c>
       <c r="O6" t="n">
-        <v>156.572555245304</v>
+        <v>156.572555167525</v>
       </c>
       <c r="P6" t="n">
-        <v>8.26315588230629</v>
+        <v>8.26315591227908</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0977634250793345</v>
+        <v>0.0977424877649973</v>
       </c>
     </row>
     <row r="7">
@@ -741,46 +741,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0633827424229261</v>
+        <v>0.0633971911045824</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0406354762877609</v>
+        <v>0.0409855379576613</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0850769041351494</v>
+        <v>0.085010334074838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0506920771075947</v>
+        <v>0.0507456406335152</v>
       </c>
       <c r="I7" t="n">
-        <v>0.212699171963716</v>
+        <v>0.212814996706958</v>
       </c>
       <c r="J7" t="n">
-        <v>0.205889870362068</v>
+        <v>0.194658691666845</v>
       </c>
       <c r="K7" t="n">
-        <v>967.615839085028</v>
+        <v>967.615837313826</v>
       </c>
       <c r="L7" t="n">
-        <v>779.645837230568</v>
+        <v>779.645847924388</v>
       </c>
       <c r="M7" t="n">
-        <v>3363.238775736</v>
+        <v>3363.23880339396</v>
       </c>
       <c r="N7" t="n">
-        <v>792.814426190649</v>
+        <v>792.814414428191</v>
       </c>
       <c r="O7" t="n">
-        <v>11.4284674478174</v>
+        <v>11.428467458169</v>
       </c>
       <c r="P7" t="n">
-        <v>0.689000044731278</v>
+        <v>0.689000107857951</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.100456111834367</v>
+        <v>0.102388542693372</v>
       </c>
     </row>
   </sheetData>
